--- a/template_instructions.xlsx
+++ b/template_instructions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenny\Desktop\sanctum - brunswick v1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenny\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9723E2F3-304E-45B4-B7F2-6A09952665CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FADFB44-BC7B-4211-B0C5-051A8B4E3E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="146" xr2:uid="{B8682349-D862-4141-AD82-F124EA4F9224}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="146" xr2:uid="{B8682349-D862-4141-AD82-F124EA4F9224}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>Replace from this</t>
   </si>
@@ -80,10 +80,25 @@
     <t>Skip this (don't apply to these)</t>
   </si>
   <si>
-    <t>Insert 'page #' or 'POS #'</t>
-  </si>
-  <si>
     <t>Select from Dropdown List: 12.08 for main spec, 8.06 for extras</t>
+  </si>
+  <si>
+    <t>Turn limiter 'A'</t>
+  </si>
+  <si>
+    <t>Telescopic stay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insert 'page #' or 'POS #'. If none, leave blank
+1) range is acceptable, eg. POS 1-3,
+2) case in-sensitive
+</t>
+  </si>
+  <si>
+    <t>Case sensitive</t>
+  </si>
+  <si>
+    <t>(same rules as above)</t>
   </si>
 </sst>
 </file>
@@ -246,7 +261,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -261,24 +276,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -305,6 +308,39 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -645,14 +681,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C80EEA1-27D5-449A-9629-F8CC5E12AA1F}">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="24.85546875" style="1" customWidth="1"/>
     <col min="7" max="7" width="36.5703125" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
@@ -664,47 +700,51 @@
       </c>
     </row>
     <row r="2" spans="1:7" s="3" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="11"/>
-      <c r="D2" s="10" t="s">
+      <c r="C2" s="24"/>
+      <c r="D2" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="21"/>
+      <c r="F2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="19" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" s="8" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" s="12" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
       <c r="F4" s="5">
@@ -764,32 +804,49 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
     </row>
-    <row r="11" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="12" spans="1:7" s="17" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="18" t="s">
+    <row r="11" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+    </row>
+    <row r="13" spans="1:7" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+    </row>
+    <row r="14" spans="1:7" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="18"/>
+    </row>
+    <row r="15" spans="1:7" s="13" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C15" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D15" s="14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-    </row>
-    <row r="14" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5"/>
@@ -801,38 +858,57 @@
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
     </row>
-    <row r="18" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:7" s="7" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19"/>
-      <c r="B19"/>
-      <c r="C19"/>
-      <c r="D19"/>
-      <c r="E19"/>
-      <c r="G19"/>
-    </row>
-    <row r="22" spans="1:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="F22" s="8" t="s">
+    <row r="18" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:7" s="6" customFormat="1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="G22"/>
+    </row>
+    <row r="25" spans="1:7" ht="15" x14ac:dyDescent="0.25">
+      <c r="F25" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F23" s="1">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F26" s="1">
         <v>12.08</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="F24" s="1">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="F27" s="1">
         <v>8.06</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="C14:D14"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F10" xr:uid="{8B9CD125-3FAF-4A4F-808E-99D045C7AE2F}">
-      <formula1>$F$23:$F$24</formula1>
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F13" xr:uid="{8B9CD125-3FAF-4A4F-808E-99D045C7AE2F}">
+      <formula1>$F$26:$F$27</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{15EBA63B-AD4D-4BF7-B54A-88125FB0D7B0}">
+      <formula1>$F$29:$F$30</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/template_instructions.xlsx
+++ b/template_instructions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jenny\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FADFB44-BC7B-4211-B0C5-051A8B4E3E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E92F07-4041-421F-9834-9A3DFBDFAB2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="146" xr2:uid="{B8682349-D862-4141-AD82-F124EA4F9224}"/>
   </bookViews>
@@ -80,32 +80,31 @@
     <t>Skip this (don't apply to these)</t>
   </si>
   <si>
-    <t>Select from Dropdown List: 12.08 for main spec, 8.06 for extras</t>
-  </si>
-  <si>
     <t>Turn limiter 'A'</t>
   </si>
   <si>
     <t>Telescopic stay</t>
   </si>
   <si>
-    <t xml:space="preserve">Insert 'page #' or 'POS #'. If none, leave blank
+    <t>Case sensitive</t>
+  </si>
+  <si>
+    <t>(same rules as above)</t>
+  </si>
+  <si>
+    <t>Insert 'page #' or 'POS #'. If none, leave blank
 1) range is acceptable, eg. POS 1-3,
-2) case in-sensitive
-</t>
-  </si>
-  <si>
-    <t>Case sensitive</t>
-  </si>
-  <si>
-    <t>(same rules as above)</t>
+2) case in-sensitive</t>
+  </si>
+  <si>
+    <t>Dropdown list: 12.08 for main spec, 8.06 for extras</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,16 +140,23 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
+      <i/>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -261,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -306,41 +312,29 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -687,10 +681,9 @@
     <col min="1" max="1" width="11.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="30" style="1" customWidth="1"/>
     <col min="3" max="3" width="27" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="36.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="1" customWidth="1"/>
+    <col min="5" max="6" width="19.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="34.42578125" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -703,18 +696,18 @@
       <c r="A2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24"/>
-      <c r="D2" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="19" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="18"/>
+      <c r="G2" s="20" t="s">
         <v>6</v>
       </c>
     </row>
@@ -725,14 +718,14 @@
       <c r="C3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="F3" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>2</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>4</v>
@@ -740,36 +733,36 @@
     </row>
     <row r="4" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5">
+        <v>8.06</v>
+      </c>
       <c r="E4" s="5"/>
-      <c r="F4" s="5">
-        <v>8.06</v>
-      </c>
+      <c r="F4" s="5"/>
       <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
       <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
+      <c r="D5" s="5">
+        <v>12.08</v>
+      </c>
       <c r="E5" s="5"/>
-      <c r="F5" s="5">
-        <v>12.08</v>
-      </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
+      <c r="D6" s="5">
+        <v>12.08</v>
+      </c>
       <c r="E6" s="5"/>
-      <c r="F6" s="5">
-        <v>12.08</v>
-      </c>
+      <c r="F6" s="5"/>
       <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -820,22 +813,15 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
     </row>
-    <row r="13" spans="1:7" s="25" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-    </row>
+    <row r="13" spans="1:7" s="2" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="1:7" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="18"/>
+      <c r="B14" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D14" s="23"/>
     </row>
     <row r="15" spans="1:7" s="13" customFormat="1" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="14" t="s">
@@ -900,15 +886,15 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="E2:F2"/>
     <mergeCell ref="C14:D14"/>
   </mergeCells>
-  <dataValidations disablePrompts="1" count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F13" xr:uid="{8B9CD125-3FAF-4A4F-808E-99D045C7AE2F}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4" xr:uid="{15EBA63B-AD4D-4BF7-B54A-88125FB0D7B0}">
+      <formula1>$F$29:$F$30</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13 D5:D12" xr:uid="{8B9CD125-3FAF-4A4F-808E-99D045C7AE2F}">
       <formula1>$F$26:$F$27</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{15EBA63B-AD4D-4BF7-B54A-88125FB0D7B0}">
-      <formula1>$F$29:$F$30</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
